--- a/APP lab archipielago 2.xlsx
+++ b/APP lab archipielago 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matias Zuñiga\Phyton lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B13783-8E9B-45D5-AA7E-4F5D17CBAA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6C4249-3A5C-4788-A71C-2A3E330B64F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Examenes Barnafi" sheetId="2" r:id="rId1"/>
@@ -10770,10 +10770,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -10819,6 +10815,10 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda [0]" xfId="1" builtinId="7"/>
@@ -10826,74 +10826,6 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{8E8CD757-F572-488D-B93A-B9557BCC45F6}"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Cambria"/>
-        <family val="1"/>
-        <scheme val="major"/>
-      </font>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Cambria"/>
-        <family val="1"/>
-        <scheme val="major"/>
-      </font>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Cambria"/>
-        <family val="1"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="6" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -11003,10 +10935,27 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Cambria"/>
+        <family val="1"/>
+        <scheme val="major"/>
+      </font>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
           <color indexed="64"/>
-        </bottom>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -11023,6 +10972,57 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Cambria"/>
+        <family val="1"/>
+        <scheme val="major"/>
+      </font>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Cambria"/>
+        <family val="1"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -11093,12 +11093,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3A28E1E-2D76-4D9E-A44D-75C38B0D568B}" name="Tabla_1" displayName="Tabla_1" ref="A1:D40" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1" headerRowBorderDxfId="7" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3A28E1E-2D76-4D9E-A44D-75C38B0D568B}" name="Tabla_1" displayName="Tabla_1" ref="A1:D40" headerRowDxfId="8" dataDxfId="6" totalsRowDxfId="4" headerRowBorderDxfId="7" tableBorderDxfId="5">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Categoría" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tema / Examen" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Protocolo / Respuesta" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Palabras Clave" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Categoría" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tema / Examen" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Protocolo / Respuesta" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Palabras Clave" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Base de Datos - Consultas Frecu-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16760,570 +16760,570 @@
   <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="41.7109375" style="201" customWidth="1"/>
-    <col min="2" max="2" width="33.5703125" style="201" customWidth="1"/>
-    <col min="3" max="3" width="37.5703125" style="201" customWidth="1"/>
-    <col min="4" max="4" width="37.5703125" style="201" hidden="1" customWidth="1"/>
-    <col min="5" max="16384" width="12.5703125" style="201"/>
+    <col min="1" max="1" width="41.7109375" style="199" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" style="199" customWidth="1"/>
+    <col min="3" max="3" width="37.5703125" style="199" customWidth="1"/>
+    <col min="4" max="4" width="37.5703125" style="199" hidden="1" customWidth="1"/>
+    <col min="5" max="16384" width="12.5703125" style="199"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="198" t="s">
+      <c r="A1" s="196" t="s">
         <v>3198</v>
       </c>
-      <c r="B1" s="199" t="s">
+      <c r="B1" s="197" t="s">
         <v>3197</v>
       </c>
-      <c r="C1" s="199" t="s">
+      <c r="C1" s="197" t="s">
         <v>1355</v>
       </c>
-      <c r="D1" s="200" t="s">
+      <c r="D1" s="198" t="s">
         <v>1354</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="202" t="s">
+      <c r="A2" s="200" t="s">
         <v>1348</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="201" t="s">
         <v>1353</v>
       </c>
-      <c r="C2" s="203" t="s">
+      <c r="C2" s="201" t="s">
         <v>1352</v>
       </c>
-      <c r="D2" s="204" t="s">
+      <c r="D2" s="202" t="s">
         <v>1351</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="202" t="s">
+      <c r="A3" s="200" t="s">
         <v>1348</v>
       </c>
-      <c r="B3" s="203" t="s">
+      <c r="B3" s="201" t="s">
         <v>1350</v>
       </c>
-      <c r="C3" s="203" t="s">
+      <c r="C3" s="201" t="s">
         <v>1349</v>
       </c>
-      <c r="D3" s="204" t="s">
+      <c r="D3" s="202" t="s">
         <v>3196</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="202" t="s">
+      <c r="A4" s="200" t="s">
         <v>1348</v>
       </c>
-      <c r="B4" s="203" t="s">
+      <c r="B4" s="201" t="s">
         <v>1347</v>
       </c>
-      <c r="C4" s="203" t="s">
+      <c r="C4" s="201" t="s">
         <v>1346</v>
       </c>
-      <c r="D4" s="204" t="s">
+      <c r="D4" s="202" t="s">
         <v>1345</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="202" t="s">
+      <c r="A5" s="200" t="s">
         <v>1348</v>
       </c>
-      <c r="B5" s="203" t="s">
+      <c r="B5" s="201" t="s">
         <v>3195</v>
       </c>
-      <c r="C5" s="203" t="s">
+      <c r="C5" s="201" t="s">
         <v>3194</v>
       </c>
-      <c r="D5" s="204" t="s">
+      <c r="D5" s="202" t="s">
         <v>3193</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="202" t="s">
+      <c r="A6" s="200" t="s">
         <v>1348</v>
       </c>
-      <c r="B6" s="203" t="s">
+      <c r="B6" s="201" t="s">
         <v>3192</v>
       </c>
-      <c r="C6" s="203" t="s">
+      <c r="C6" s="201" t="s">
         <v>3191</v>
       </c>
-      <c r="D6" s="204" t="s">
+      <c r="D6" s="202" t="s">
         <v>3190</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="202" t="s">
+      <c r="A7" s="200" t="s">
         <v>1348</v>
       </c>
-      <c r="B7" s="203" t="s">
+      <c r="B7" s="201" t="s">
         <v>3189</v>
       </c>
-      <c r="C7" s="203" t="s">
+      <c r="C7" s="201" t="s">
         <v>3188</v>
       </c>
-      <c r="D7" s="204" t="s">
+      <c r="D7" s="202" t="s">
         <v>3187</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="202" t="s">
+      <c r="A8" s="200" t="s">
         <v>1348</v>
       </c>
-      <c r="B8" s="203" t="s">
+      <c r="B8" s="201" t="s">
         <v>3186</v>
       </c>
-      <c r="C8" s="203" t="s">
+      <c r="C8" s="201" t="s">
         <v>3185</v>
       </c>
-      <c r="D8" s="204" t="s">
+      <c r="D8" s="202" t="s">
         <v>3184</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="202" t="s">
+      <c r="A9" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B9" s="203" t="s">
+      <c r="B9" s="201" t="s">
         <v>1344</v>
       </c>
-      <c r="C9" s="203" t="s">
+      <c r="C9" s="201" t="s">
         <v>1343</v>
       </c>
-      <c r="D9" s="204" t="s">
+      <c r="D9" s="202" t="s">
         <v>1342</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="202" t="s">
+      <c r="A10" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B10" s="203" t="s">
+      <c r="B10" s="201" t="s">
         <v>3183</v>
       </c>
-      <c r="C10" s="203" t="s">
+      <c r="C10" s="201" t="s">
         <v>3199</v>
       </c>
-      <c r="D10" s="204" t="s">
+      <c r="D10" s="202" t="s">
         <v>1341</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="202" t="s">
+      <c r="A11" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B11" s="203" t="s">
+      <c r="B11" s="201" t="s">
         <v>3182</v>
       </c>
-      <c r="C11" s="203" t="s">
+      <c r="C11" s="201" t="s">
         <v>1340</v>
       </c>
-      <c r="D11" s="204" t="s">
+      <c r="D11" s="202" t="s">
         <v>1339</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="202" t="s">
+      <c r="A12" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B12" s="203" t="s">
+      <c r="B12" s="201" t="s">
         <v>1338</v>
       </c>
-      <c r="C12" s="203" t="s">
+      <c r="C12" s="201" t="s">
         <v>3181</v>
       </c>
-      <c r="D12" s="204" t="s">
+      <c r="D12" s="202" t="s">
         <v>3180</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="202" t="s">
+      <c r="A13" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B13" s="203" t="s">
+      <c r="B13" s="201" t="s">
         <v>1336</v>
       </c>
-      <c r="C13" s="203" t="s">
+      <c r="C13" s="201" t="s">
         <v>1335</v>
       </c>
-      <c r="D13" s="204" t="s">
+      <c r="D13" s="202" t="s">
         <v>1334</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="202" t="s">
+      <c r="A14" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B14" s="203" t="s">
+      <c r="B14" s="201" t="s">
         <v>3179</v>
       </c>
-      <c r="C14" s="203" t="s">
+      <c r="C14" s="201" t="s">
         <v>3178</v>
       </c>
-      <c r="D14" s="204" t="s">
+      <c r="D14" s="202" t="s">
         <v>3177</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="202" t="s">
+      <c r="A15" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B15" s="203" t="s">
+      <c r="B15" s="201" t="s">
         <v>3176</v>
       </c>
-      <c r="C15" s="203" t="s">
+      <c r="C15" s="201" t="s">
         <v>3175</v>
       </c>
-      <c r="D15" s="204" t="s">
+      <c r="D15" s="202" t="s">
         <v>3174</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="202" t="s">
+      <c r="A16" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B16" s="203" t="s">
+      <c r="B16" s="201" t="s">
         <v>3173</v>
       </c>
-      <c r="C16" s="203" t="s">
+      <c r="C16" s="201" t="s">
         <v>3172</v>
       </c>
-      <c r="D16" s="204" t="s">
+      <c r="D16" s="202" t="s">
         <v>3171</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202" t="s">
+      <c r="A17" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B17" s="203" t="s">
+      <c r="B17" s="201" t="s">
         <v>3170</v>
       </c>
-      <c r="C17" s="203" t="s">
+      <c r="C17" s="201" t="s">
         <v>3169</v>
       </c>
-      <c r="D17" s="204" t="s">
+      <c r="D17" s="202" t="s">
         <v>3168</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="202" t="s">
+      <c r="A18" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B18" s="208" t="s">
+      <c r="B18" s="206" t="s">
         <v>3200</v>
       </c>
-      <c r="C18" s="209" t="s">
+      <c r="C18" s="207" t="s">
         <v>2955</v>
       </c>
-      <c r="D18" s="209" t="s">
+      <c r="D18" s="207" t="s">
         <v>2954</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="202" t="s">
+      <c r="A19" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B19" s="203" t="s">
+      <c r="B19" s="201" t="s">
         <v>3167</v>
       </c>
-      <c r="C19" s="203" t="s">
+      <c r="C19" s="201" t="s">
         <v>3166</v>
       </c>
-      <c r="D19" s="204" t="s">
+      <c r="D19" s="202" t="s">
         <v>3165</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="202" t="s">
+      <c r="A20" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B20" s="203" t="s">
+      <c r="B20" s="201" t="s">
         <v>3164</v>
       </c>
-      <c r="C20" s="203" t="s">
+      <c r="C20" s="201" t="s">
         <v>3163</v>
       </c>
-      <c r="D20" s="204" t="s">
+      <c r="D20" s="202" t="s">
         <v>3162</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="202" t="s">
+      <c r="A21" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B21" s="203" t="s">
+      <c r="B21" s="201" t="s">
         <v>3161</v>
       </c>
-      <c r="C21" s="203" t="s">
+      <c r="C21" s="201" t="s">
         <v>3160</v>
       </c>
-      <c r="D21" s="204" t="s">
+      <c r="D21" s="202" t="s">
         <v>3159</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="202" t="s">
+      <c r="A22" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B22" s="203" t="s">
+      <c r="B22" s="201" t="s">
         <v>3158</v>
       </c>
-      <c r="C22" s="203" t="s">
+      <c r="C22" s="201" t="s">
         <v>3157</v>
       </c>
-      <c r="D22" s="204" t="s">
+      <c r="D22" s="202" t="s">
         <v>3156</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="202" t="s">
+      <c r="A23" s="200" t="s">
         <v>1337</v>
       </c>
-      <c r="B23" s="203" t="s">
+      <c r="B23" s="201" t="s">
         <v>3155</v>
       </c>
-      <c r="C23" s="203" t="s">
+      <c r="C23" s="201" t="s">
         <v>3154</v>
       </c>
-      <c r="D23" s="204" t="s">
+      <c r="D23" s="202" t="s">
         <v>3153</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="202" t="s">
+      <c r="A24" s="200" t="s">
         <v>3149</v>
       </c>
-      <c r="B24" s="203" t="s">
+      <c r="B24" s="201" t="s">
         <v>3152</v>
       </c>
-      <c r="C24" s="203" t="s">
+      <c r="C24" s="201" t="s">
         <v>3151</v>
       </c>
-      <c r="D24" s="204" t="s">
+      <c r="D24" s="202" t="s">
         <v>3150</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="202" t="s">
+      <c r="A25" s="200" t="s">
         <v>3149</v>
       </c>
-      <c r="B25" s="203" t="s">
+      <c r="B25" s="201" t="s">
         <v>3148</v>
       </c>
-      <c r="C25" s="203" t="s">
+      <c r="C25" s="201" t="s">
         <v>3147</v>
       </c>
-      <c r="D25" s="204" t="s">
+      <c r="D25" s="202" t="s">
         <v>3146</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="202" t="s">
+      <c r="A26" s="200" t="s">
         <v>1333</v>
       </c>
-      <c r="B26" s="203" t="s">
+      <c r="B26" s="201" t="s">
         <v>1332</v>
       </c>
-      <c r="C26" s="203" t="s">
+      <c r="C26" s="201" t="s">
         <v>1331</v>
       </c>
-      <c r="D26" s="204" t="s">
+      <c r="D26" s="202" t="s">
         <v>3145</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="202" t="s">
+      <c r="A27" s="200" t="s">
         <v>1333</v>
       </c>
-      <c r="B27" s="203" t="s">
+      <c r="B27" s="201" t="s">
         <v>3144</v>
       </c>
-      <c r="C27" s="203" t="s">
+      <c r="C27" s="201" t="s">
         <v>3143</v>
       </c>
-      <c r="D27" s="204" t="s">
+      <c r="D27" s="202" t="s">
         <v>3142</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="202" t="s">
+      <c r="A28" s="200" t="s">
         <v>3123</v>
       </c>
-      <c r="B28" s="203" t="s">
+      <c r="B28" s="201" t="s">
         <v>3141</v>
       </c>
-      <c r="C28" s="203" t="s">
+      <c r="C28" s="201" t="s">
         <v>3140</v>
       </c>
-      <c r="D28" s="204" t="s">
+      <c r="D28" s="202" t="s">
         <v>3139</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="202" t="s">
+      <c r="A29" s="200" t="s">
         <v>3123</v>
       </c>
-      <c r="B29" s="203" t="s">
+      <c r="B29" s="201" t="s">
         <v>3138</v>
       </c>
-      <c r="C29" s="203" t="s">
+      <c r="C29" s="201" t="s">
         <v>3137</v>
       </c>
-      <c r="D29" s="204" t="s">
+      <c r="D29" s="202" t="s">
         <v>3136</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="202" t="s">
+      <c r="A30" s="200" t="s">
         <v>3123</v>
       </c>
-      <c r="B30" s="203" t="s">
+      <c r="B30" s="201" t="s">
         <v>3135</v>
       </c>
-      <c r="C30" s="203" t="s">
+      <c r="C30" s="201" t="s">
         <v>3134</v>
       </c>
-      <c r="D30" s="204" t="s">
+      <c r="D30" s="202" t="s">
         <v>3133</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="202" t="s">
+      <c r="A31" s="200" t="s">
         <v>3123</v>
       </c>
-      <c r="B31" s="203" t="s">
+      <c r="B31" s="201" t="s">
         <v>3132</v>
       </c>
-      <c r="C31" s="203" t="s">
+      <c r="C31" s="201" t="s">
         <v>3131</v>
       </c>
-      <c r="D31" s="204" t="s">
+      <c r="D31" s="202" t="s">
         <v>3130</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="202" t="s">
+      <c r="A32" s="200" t="s">
         <v>3123</v>
       </c>
-      <c r="B32" s="203" t="s">
+      <c r="B32" s="201" t="s">
         <v>3129</v>
       </c>
-      <c r="C32" s="203" t="s">
+      <c r="C32" s="201" t="s">
         <v>3128</v>
       </c>
-      <c r="D32" s="204" t="s">
+      <c r="D32" s="202" t="s">
         <v>3127</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="202" t="s">
+      <c r="A33" s="200" t="s">
         <v>3123</v>
       </c>
-      <c r="B33" s="203" t="s">
+      <c r="B33" s="201" t="s">
         <v>3126</v>
       </c>
-      <c r="C33" s="203" t="s">
+      <c r="C33" s="201" t="s">
         <v>3125</v>
       </c>
-      <c r="D33" s="204" t="s">
+      <c r="D33" s="202" t="s">
         <v>3124</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="202" t="s">
+      <c r="A34" s="200" t="s">
         <v>3123</v>
       </c>
-      <c r="B34" s="203" t="s">
+      <c r="B34" s="201" t="s">
         <v>3122</v>
       </c>
-      <c r="C34" s="203" t="s">
+      <c r="C34" s="201" t="s">
         <v>3121</v>
       </c>
-      <c r="D34" s="204" t="s">
+      <c r="D34" s="202" t="s">
         <v>3120</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="202" t="s">
+      <c r="A35" s="200" t="s">
         <v>1330</v>
       </c>
-      <c r="B35" s="203" t="s">
+      <c r="B35" s="201" t="s">
         <v>3119</v>
       </c>
-      <c r="C35" s="203" t="s">
+      <c r="C35" s="201" t="s">
         <v>3118</v>
       </c>
-      <c r="D35" s="204" t="s">
+      <c r="D35" s="202" t="s">
         <v>3117</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="202" t="s">
+      <c r="A36" s="200" t="s">
         <v>1330</v>
       </c>
-      <c r="B36" s="203" t="s">
+      <c r="B36" s="201" t="s">
         <v>1329</v>
       </c>
-      <c r="C36" s="203" t="s">
+      <c r="C36" s="201" t="s">
         <v>3116</v>
       </c>
-      <c r="D36" s="204" t="s">
+      <c r="D36" s="202" t="s">
         <v>1328</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="202" t="s">
+      <c r="A37" s="200" t="s">
         <v>1330</v>
       </c>
-      <c r="B37" s="203" t="s">
+      <c r="B37" s="201" t="s">
         <v>3115</v>
       </c>
-      <c r="C37" s="203" t="s">
+      <c r="C37" s="201" t="s">
         <v>3114</v>
       </c>
-      <c r="D37" s="204" t="s">
+      <c r="D37" s="202" t="s">
         <v>3113</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="202" t="s">
+      <c r="A38" s="200" t="s">
         <v>1327</v>
       </c>
-      <c r="B38" s="203" t="s">
+      <c r="B38" s="201" t="s">
         <v>3112</v>
       </c>
-      <c r="C38" s="203" t="s">
+      <c r="C38" s="201" t="s">
         <v>1326</v>
       </c>
-      <c r="D38" s="204" t="s">
+      <c r="D38" s="202" t="s">
         <v>1325</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="202" t="s">
+      <c r="A39" s="200" t="s">
         <v>1327</v>
       </c>
-      <c r="B39" s="203" t="s">
+      <c r="B39" s="201" t="s">
         <v>3111</v>
       </c>
-      <c r="C39" s="203" t="s">
+      <c r="C39" s="201" t="s">
         <v>3110</v>
       </c>
-      <c r="D39" s="204" t="s">
+      <c r="D39" s="202" t="s">
         <v>3109</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="205" t="s">
+      <c r="A40" s="203" t="s">
         <v>1327</v>
       </c>
-      <c r="B40" s="206" t="s">
+      <c r="B40" s="204" t="s">
         <v>3108</v>
       </c>
-      <c r="C40" s="206" t="s">
+      <c r="C40" s="204" t="s">
         <v>3107</v>
       </c>
-      <c r="D40" s="207" t="s">
+      <c r="D40" s="205" t="s">
         <v>3106</v>
       </c>
     </row>
@@ -17366,12 +17366,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="193" t="s">
+      <c r="A2" s="208" t="s">
         <v>1406</v>
       </c>
-      <c r="B2" s="194"/>
-      <c r="C2" s="194"/>
-      <c r="D2" s="194"/>
+      <c r="B2" s="209"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="209"/>
     </row>
     <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -17430,12 +17430,12 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="193" t="s">
+      <c r="A7" s="208" t="s">
         <v>1393</v>
       </c>
-      <c r="B7" s="194"/>
-      <c r="C7" s="194"/>
-      <c r="D7" s="194"/>
+      <c r="B7" s="209"/>
+      <c r="C7" s="209"/>
+      <c r="D7" s="209"/>
     </row>
     <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
@@ -17480,12 +17480,12 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="193" t="s">
+      <c r="A11" s="208" t="s">
         <v>1381</v>
       </c>
-      <c r="B11" s="194"/>
-      <c r="C11" s="194"/>
-      <c r="D11" s="194"/>
+      <c r="B11" s="209"/>
+      <c r="C11" s="209"/>
+      <c r="D11" s="209"/>
     </row>
     <row r="12" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
@@ -17530,12 +17530,12 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="193" t="s">
+      <c r="A15" s="208" t="s">
         <v>1371</v>
       </c>
-      <c r="B15" s="194"/>
-      <c r="C15" s="194"/>
-      <c r="D15" s="194"/>
+      <c r="B15" s="209"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="209"/>
     </row>
     <row r="16" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
@@ -17552,12 +17552,12 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="193" t="s">
+      <c r="A17" s="208" t="s">
         <v>1366</v>
       </c>
-      <c r="B17" s="194"/>
-      <c r="C17" s="194"/>
-      <c r="D17" s="194"/>
+      <c r="B17" s="209"/>
+      <c r="C17" s="209"/>
+      <c r="D17" s="209"/>
     </row>
     <row r="18" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
@@ -52318,622 +52318,622 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="197" t="s">
+      <c r="A1" s="195" t="s">
         <v>3105</v>
       </c>
-      <c r="B1" s="197" t="s">
+      <c r="B1" s="195" t="s">
         <v>3104</v>
       </c>
-      <c r="C1" s="197" t="s">
+      <c r="C1" s="195" t="s">
         <v>3103</v>
       </c>
-      <c r="D1" s="197" t="s">
+      <c r="D1" s="195" t="s">
         <v>2944</v>
       </c>
-      <c r="E1" s="197" t="s">
+      <c r="E1" s="195" t="s">
         <v>3102</v>
       </c>
-      <c r="F1" s="197" t="s">
+      <c r="F1" s="195" t="s">
         <v>3101</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="195" t="s">
+      <c r="A2" s="193" t="s">
         <v>3100</v>
       </c>
-      <c r="B2" s="195" t="s">
+      <c r="B2" s="193" t="s">
         <v>3029</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="193" t="s">
         <v>3099</v>
       </c>
-      <c r="D2" s="195" t="s">
+      <c r="D2" s="193" t="s">
         <v>3098</v>
       </c>
-      <c r="E2" s="195" t="s">
+      <c r="E2" s="193" t="s">
         <v>3097</v>
       </c>
-      <c r="F2" s="195" t="s">
+      <c r="F2" s="193" t="s">
         <v>3096</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="196" t="s">
+      <c r="A3" s="194" t="s">
         <v>3095</v>
       </c>
-      <c r="B3" s="196" t="s">
+      <c r="B3" s="194" t="s">
         <v>3040</v>
       </c>
-      <c r="C3" s="196" t="s">
+      <c r="C3" s="194" t="s">
         <v>3014</v>
       </c>
-      <c r="D3" s="196" t="s">
+      <c r="D3" s="194" t="s">
         <v>3081</v>
       </c>
-      <c r="E3" s="196" t="s">
+      <c r="E3" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F3" s="196" t="s">
+      <c r="F3" s="194" t="s">
         <v>3094</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A4" s="195" t="s">
+      <c r="A4" s="193" t="s">
         <v>3093</v>
       </c>
-      <c r="B4" s="195" t="s">
+      <c r="B4" s="193" t="s">
         <v>3092</v>
       </c>
-      <c r="C4" s="195" t="s">
+      <c r="C4" s="193" t="s">
         <v>3014</v>
       </c>
-      <c r="D4" s="195" t="s">
+      <c r="D4" s="193" t="s">
         <v>3065</v>
       </c>
-      <c r="E4" s="195" t="s">
+      <c r="E4" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F4" s="195" t="s">
+      <c r="F4" s="193" t="s">
         <v>3091</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="195" x14ac:dyDescent="0.25">
-      <c r="A5" s="196" t="s">
+      <c r="A5" s="194" t="s">
         <v>3090</v>
       </c>
-      <c r="B5" s="196" t="s">
+      <c r="B5" s="194" t="s">
         <v>3089</v>
       </c>
-      <c r="C5" s="196" t="s">
+      <c r="C5" s="194" t="s">
         <v>3014</v>
       </c>
-      <c r="D5" s="196" t="s">
+      <c r="D5" s="194" t="s">
         <v>3088</v>
       </c>
-      <c r="E5" s="196" t="s">
+      <c r="E5" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F5" s="196" t="s">
+      <c r="F5" s="194" t="s">
         <v>3087</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A6" s="195" t="s">
+      <c r="A6" s="193" t="s">
         <v>3086</v>
       </c>
-      <c r="B6" s="195" t="s">
+      <c r="B6" s="193" t="s">
         <v>3085</v>
       </c>
-      <c r="C6" s="195" t="s">
+      <c r="C6" s="193" t="s">
         <v>3014</v>
       </c>
-      <c r="D6" s="195" t="s">
+      <c r="D6" s="193" t="s">
         <v>3081</v>
       </c>
-      <c r="E6" s="195" t="s">
+      <c r="E6" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F6" s="195" t="s">
+      <c r="F6" s="193" t="s">
         <v>3084</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="165" x14ac:dyDescent="0.25">
-      <c r="A7" s="196" t="s">
+      <c r="A7" s="194" t="s">
         <v>3083</v>
       </c>
-      <c r="B7" s="196" t="s">
+      <c r="B7" s="194" t="s">
         <v>3082</v>
       </c>
-      <c r="C7" s="196" t="s">
+      <c r="C7" s="194" t="s">
         <v>3014</v>
       </c>
-      <c r="D7" s="196" t="s">
+      <c r="D7" s="194" t="s">
         <v>3081</v>
       </c>
-      <c r="E7" s="196" t="s">
+      <c r="E7" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F7" s="196" t="s">
+      <c r="F7" s="194" t="s">
         <v>3080</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="195" t="s">
+      <c r="A8" s="193" t="s">
         <v>3079</v>
       </c>
-      <c r="B8" s="195" t="s">
+      <c r="B8" s="193" t="s">
         <v>3078</v>
       </c>
-      <c r="C8" s="195" t="s">
+      <c r="C8" s="193" t="s">
         <v>3014</v>
       </c>
-      <c r="D8" s="195" t="s">
+      <c r="D8" s="193" t="s">
         <v>2223</v>
       </c>
-      <c r="E8" s="195" t="s">
+      <c r="E8" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F8" s="195"/>
+      <c r="F8" s="193"/>
     </row>
     <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="196" t="s">
+      <c r="A9" s="194" t="s">
         <v>3077</v>
       </c>
-      <c r="B9" s="196" t="s">
+      <c r="B9" s="194" t="s">
         <v>3076</v>
       </c>
-      <c r="C9" s="196" t="s">
+      <c r="C9" s="194" t="s">
         <v>3014</v>
       </c>
-      <c r="D9" s="196" t="s">
+      <c r="D9" s="194" t="s">
         <v>2223</v>
       </c>
-      <c r="E9" s="196" t="s">
+      <c r="E9" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F9" s="196" t="s">
+      <c r="F9" s="194" t="s">
         <v>3075</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="195" t="s">
+      <c r="A10" s="193" t="s">
         <v>3074</v>
       </c>
-      <c r="B10" s="195" t="s">
+      <c r="B10" s="193" t="s">
         <v>3073</v>
       </c>
-      <c r="C10" s="195" t="s">
+      <c r="C10" s="193" t="s">
         <v>3014</v>
       </c>
-      <c r="D10" s="195" t="s">
+      <c r="D10" s="193" t="s">
         <v>3072</v>
       </c>
-      <c r="E10" s="195" t="s">
+      <c r="E10" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F10" s="195" t="s">
+      <c r="F10" s="193" t="s">
         <v>3071</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="196" t="s">
+      <c r="A11" s="194" t="s">
         <v>3070</v>
       </c>
-      <c r="B11" s="196" t="s">
+      <c r="B11" s="194" t="s">
         <v>3069</v>
       </c>
-      <c r="C11" s="196" t="s">
+      <c r="C11" s="194" t="s">
         <v>3014</v>
       </c>
-      <c r="D11" s="196" t="s">
+      <c r="D11" s="194" t="s">
         <v>2223</v>
       </c>
-      <c r="E11" s="196" t="s">
+      <c r="E11" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F11" s="196"/>
+      <c r="F11" s="194"/>
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="195" t="s">
+      <c r="A12" s="193" t="s">
         <v>3068</v>
       </c>
-      <c r="B12" s="195" t="s">
+      <c r="B12" s="193" t="s">
         <v>3062</v>
       </c>
-      <c r="C12" s="195" t="s">
+      <c r="C12" s="193" t="s">
         <v>3028</v>
       </c>
-      <c r="D12" s="195" t="s">
+      <c r="D12" s="193" t="s">
         <v>3027</v>
       </c>
-      <c r="E12" s="195" t="s">
+      <c r="E12" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F12" s="195" t="s">
+      <c r="F12" s="193" t="s">
         <v>3032</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="196" t="s">
+      <c r="A13" s="194" t="s">
         <v>3067</v>
       </c>
-      <c r="B13" s="196" t="s">
+      <c r="B13" s="194" t="s">
         <v>3066</v>
       </c>
-      <c r="C13" s="196" t="s">
+      <c r="C13" s="194" t="s">
         <v>3014</v>
       </c>
-      <c r="D13" s="196" t="s">
+      <c r="D13" s="194" t="s">
         <v>3065</v>
       </c>
-      <c r="E13" s="196" t="s">
+      <c r="E13" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F13" s="196"/>
+      <c r="F13" s="194"/>
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="195" t="s">
+      <c r="A14" s="193" t="s">
         <v>3064</v>
       </c>
-      <c r="B14" s="195" t="s">
+      <c r="B14" s="193" t="s">
         <v>3040</v>
       </c>
-      <c r="C14" s="195" t="s">
+      <c r="C14" s="193" t="s">
         <v>3014</v>
       </c>
-      <c r="D14" s="195" t="s">
+      <c r="D14" s="193" t="s">
         <v>3036</v>
       </c>
-      <c r="E14" s="195" t="s">
+      <c r="E14" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F14" s="195"/>
+      <c r="F14" s="193"/>
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="196" t="s">
+      <c r="A15" s="194" t="s">
         <v>3063</v>
       </c>
-      <c r="B15" s="196" t="s">
+      <c r="B15" s="194" t="s">
         <v>3062</v>
       </c>
-      <c r="C15" s="196" t="s">
+      <c r="C15" s="194" t="s">
         <v>3028</v>
       </c>
-      <c r="D15" s="196" t="s">
+      <c r="D15" s="194" t="s">
         <v>3027</v>
       </c>
-      <c r="E15" s="196" t="s">
+      <c r="E15" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F15" s="196" t="s">
+      <c r="F15" s="194" t="s">
         <v>3032</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="195" t="s">
+      <c r="A16" s="193" t="s">
         <v>3061</v>
       </c>
-      <c r="B16" s="195" t="s">
+      <c r="B16" s="193" t="s">
         <v>3060</v>
       </c>
-      <c r="C16" s="195" t="s">
+      <c r="C16" s="193" t="s">
         <v>3014</v>
       </c>
-      <c r="D16" s="195" t="s">
+      <c r="D16" s="193" t="s">
         <v>3059</v>
       </c>
-      <c r="E16" s="195" t="s">
+      <c r="E16" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F16" s="195"/>
+      <c r="F16" s="193"/>
     </row>
     <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="196" t="s">
+      <c r="A17" s="194" t="s">
         <v>3058</v>
       </c>
-      <c r="B17" s="196" t="s">
+      <c r="B17" s="194" t="s">
         <v>3057</v>
       </c>
-      <c r="C17" s="196" t="s">
+      <c r="C17" s="194" t="s">
         <v>3014</v>
       </c>
-      <c r="D17" s="196" t="s">
+      <c r="D17" s="194" t="s">
         <v>3056</v>
       </c>
-      <c r="E17" s="196" t="s">
+      <c r="E17" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F17" s="196"/>
+      <c r="F17" s="194"/>
     </row>
     <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="195" t="s">
+      <c r="A18" s="193" t="s">
         <v>3055</v>
       </c>
-      <c r="B18" s="195" t="s">
+      <c r="B18" s="193" t="s">
         <v>3040</v>
       </c>
-      <c r="C18" s="195" t="s">
+      <c r="C18" s="193" t="s">
         <v>3014</v>
       </c>
-      <c r="D18" s="195" t="s">
+      <c r="D18" s="193" t="s">
         <v>3053</v>
       </c>
-      <c r="E18" s="195" t="s">
+      <c r="E18" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F18" s="195"/>
+      <c r="F18" s="193"/>
     </row>
     <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="196" t="s">
+      <c r="A19" s="194" t="s">
         <v>3054</v>
       </c>
-      <c r="B19" s="196" t="s">
+      <c r="B19" s="194" t="s">
         <v>3040</v>
       </c>
-      <c r="C19" s="196" t="s">
+      <c r="C19" s="194" t="s">
         <v>3014</v>
       </c>
-      <c r="D19" s="196" t="s">
+      <c r="D19" s="194" t="s">
         <v>3053</v>
       </c>
-      <c r="E19" s="196" t="s">
+      <c r="E19" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F19" s="196"/>
+      <c r="F19" s="194"/>
     </row>
     <row r="20" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="195" t="s">
+      <c r="A20" s="193" t="s">
         <v>3052</v>
       </c>
-      <c r="B20" s="195" t="s">
+      <c r="B20" s="193" t="s">
         <v>3051</v>
       </c>
-      <c r="C20" s="195" t="s">
+      <c r="C20" s="193" t="s">
         <v>3034</v>
       </c>
-      <c r="D20" s="195" t="s">
+      <c r="D20" s="193" t="s">
         <v>3050</v>
       </c>
-      <c r="E20" s="195" t="s">
+      <c r="E20" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F20" s="195" t="s">
+      <c r="F20" s="193" t="s">
         <v>3032</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="196" t="s">
+      <c r="A21" s="194" t="s">
         <v>3049</v>
       </c>
-      <c r="B21" s="196" t="s">
+      <c r="B21" s="194" t="s">
         <v>3048</v>
       </c>
-      <c r="C21" s="196" t="s">
+      <c r="C21" s="194" t="s">
         <v>3028</v>
       </c>
-      <c r="D21" s="196" t="s">
+      <c r="D21" s="194" t="s">
         <v>3027</v>
       </c>
-      <c r="E21" s="196" t="s">
+      <c r="E21" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F21" s="196" t="s">
+      <c r="F21" s="194" t="s">
         <v>3032</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="195" t="s">
+      <c r="A22" s="193" t="s">
         <v>1208</v>
       </c>
-      <c r="B22" s="195" t="s">
+      <c r="B22" s="193" t="s">
         <v>3047</v>
       </c>
-      <c r="C22" s="195" t="s">
+      <c r="C22" s="193" t="s">
         <v>3028</v>
       </c>
-      <c r="D22" s="195" t="s">
+      <c r="D22" s="193" t="s">
         <v>3027</v>
       </c>
-      <c r="E22" s="195" t="s">
+      <c r="E22" s="193" t="s">
         <v>3042</v>
       </c>
-      <c r="F22" s="195" t="s">
+      <c r="F22" s="193" t="s">
         <v>3032</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="196" t="s">
+      <c r="A23" s="194" t="s">
         <v>3046</v>
       </c>
-      <c r="B23" s="196" t="s">
+      <c r="B23" s="194" t="s">
         <v>3045</v>
       </c>
-      <c r="C23" s="196" t="s">
+      <c r="C23" s="194" t="s">
         <v>3044</v>
       </c>
-      <c r="D23" s="196" t="s">
+      <c r="D23" s="194" t="s">
         <v>3043</v>
       </c>
-      <c r="E23" s="196" t="s">
+      <c r="E23" s="194" t="s">
         <v>3042</v>
       </c>
-      <c r="F23" s="196" t="s">
+      <c r="F23" s="194" t="s">
         <v>3032</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="195" t="s">
+      <c r="A24" s="193" t="s">
         <v>3041</v>
       </c>
-      <c r="B24" s="195" t="s">
+      <c r="B24" s="193" t="s">
         <v>3040</v>
       </c>
-      <c r="C24" s="195" t="s">
+      <c r="C24" s="193" t="s">
         <v>3014</v>
       </c>
-      <c r="D24" s="195" t="s">
+      <c r="D24" s="193" t="s">
         <v>3036</v>
       </c>
-      <c r="E24" s="195" t="s">
+      <c r="E24" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F24" s="195"/>
+      <c r="F24" s="193"/>
     </row>
     <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="196" t="s">
+      <c r="A25" s="194" t="s">
         <v>3039</v>
       </c>
-      <c r="B25" s="196" t="s">
+      <c r="B25" s="194" t="s">
         <v>3024</v>
       </c>
-      <c r="C25" s="196" t="s">
+      <c r="C25" s="194" t="s">
         <v>3034</v>
       </c>
-      <c r="D25" s="196" t="s">
+      <c r="D25" s="194" t="s">
         <v>3033</v>
       </c>
-      <c r="E25" s="196" t="s">
+      <c r="E25" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F25" s="196" t="s">
+      <c r="F25" s="194" t="s">
         <v>3032</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="195" t="s">
+      <c r="A26" s="193" t="s">
         <v>3038</v>
       </c>
-      <c r="B26" s="195" t="s">
+      <c r="B26" s="193" t="s">
         <v>3037</v>
       </c>
-      <c r="C26" s="195" t="s">
+      <c r="C26" s="193" t="s">
         <v>3014</v>
       </c>
-      <c r="D26" s="195" t="s">
+      <c r="D26" s="193" t="s">
         <v>3036</v>
       </c>
-      <c r="E26" s="195" t="s">
+      <c r="E26" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F26" s="195"/>
+      <c r="F26" s="193"/>
     </row>
     <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="196" t="s">
+      <c r="A27" s="194" t="s">
         <v>3035</v>
       </c>
-      <c r="B27" s="196" t="s">
+      <c r="B27" s="194" t="s">
         <v>3024</v>
       </c>
-      <c r="C27" s="196" t="s">
+      <c r="C27" s="194" t="s">
         <v>3034</v>
       </c>
-      <c r="D27" s="196" t="s">
+      <c r="D27" s="194" t="s">
         <v>3033</v>
       </c>
-      <c r="E27" s="196" t="s">
+      <c r="E27" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F27" s="196" t="s">
+      <c r="F27" s="194" t="s">
         <v>3032</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="195" t="s">
+      <c r="A28" s="193" t="s">
         <v>3031</v>
       </c>
-      <c r="B28" s="195" t="s">
+      <c r="B28" s="193" t="s">
         <v>3029</v>
       </c>
-      <c r="C28" s="195" t="s">
+      <c r="C28" s="193" t="s">
         <v>3028</v>
       </c>
-      <c r="D28" s="195" t="s">
+      <c r="D28" s="193" t="s">
         <v>3027</v>
       </c>
-      <c r="E28" s="195" t="s">
+      <c r="E28" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F28" s="195" t="s">
+      <c r="F28" s="193" t="s">
         <v>3026</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A29" s="196" t="s">
+      <c r="A29" s="194" t="s">
         <v>3030</v>
       </c>
-      <c r="B29" s="196" t="s">
+      <c r="B29" s="194" t="s">
         <v>3029</v>
       </c>
-      <c r="C29" s="196" t="s">
+      <c r="C29" s="194" t="s">
         <v>3028</v>
       </c>
-      <c r="D29" s="196" t="s">
+      <c r="D29" s="194" t="s">
         <v>3027</v>
       </c>
-      <c r="E29" s="196" t="s">
+      <c r="E29" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F29" s="196" t="s">
+      <c r="F29" s="194" t="s">
         <v>3026</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="195" t="s">
+      <c r="A30" s="193" t="s">
         <v>3025</v>
       </c>
-      <c r="B30" s="195" t="s">
+      <c r="B30" s="193" t="s">
         <v>3024</v>
       </c>
-      <c r="C30" s="195" t="s">
+      <c r="C30" s="193" t="s">
         <v>3023</v>
       </c>
-      <c r="D30" s="195" t="s">
+      <c r="D30" s="193" t="s">
         <v>3022</v>
       </c>
-      <c r="E30" s="195" t="s">
+      <c r="E30" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F30" s="195" t="s">
+      <c r="F30" s="193" t="s">
         <v>3021</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="196" t="s">
+      <c r="A31" s="194" t="s">
         <v>3020</v>
       </c>
-      <c r="B31" s="196" t="s">
+      <c r="B31" s="194" t="s">
         <v>3019</v>
       </c>
-      <c r="C31" s="196" t="s">
+      <c r="C31" s="194" t="s">
         <v>3014</v>
       </c>
-      <c r="D31" s="196" t="s">
+      <c r="D31" s="194" t="s">
         <v>3018</v>
       </c>
-      <c r="E31" s="196" t="s">
+      <c r="E31" s="194" t="s">
         <v>3012</v>
       </c>
-      <c r="F31" s="196" t="s">
+      <c r="F31" s="194" t="s">
         <v>3017</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A32" s="195" t="s">
+      <c r="A32" s="193" t="s">
         <v>3016</v>
       </c>
-      <c r="B32" s="195" t="s">
+      <c r="B32" s="193" t="s">
         <v>3015</v>
       </c>
-      <c r="C32" s="195" t="s">
+      <c r="C32" s="193" t="s">
         <v>3014</v>
       </c>
-      <c r="D32" s="195" t="s">
+      <c r="D32" s="193" t="s">
         <v>3013</v>
       </c>
-      <c r="E32" s="195" t="s">
+      <c r="E32" s="193" t="s">
         <v>3012</v>
       </c>
-      <c r="F32" s="195" t="s">
+      <c r="F32" s="193" t="s">
         <v>3011</v>
       </c>
     </row>

--- a/APP lab archipielago 2.xlsx
+++ b/APP lab archipielago 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matias Zuñiga\Phyton lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6C4249-3A5C-4788-A71C-2A3E330B64F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144BF16D-DF9F-404F-8EED-1AFB0018A537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9703,9 +9703,6 @@
     <t>Si la muestra presenta coágulos (tubo morado o rojo), se rechaza inmediatamente y se solicita nueva toma al paciente.</t>
   </si>
   <si>
-    <t>Muestra Coagulada (Hemograma / Tubos)</t>
-  </si>
-  <si>
     <t>rechazo, muestra, rotular, nombre, tubo morado, llenado, vhs, coagulo</t>
   </si>
   <si>
@@ -9767,6 +9764,9 @@
   </si>
   <si>
     <t>Deposicion fresca para test FOB (hemorragia oculta), Helicobacter pylori, Calprotectina, leucocitos feacales</t>
+  </si>
+  <si>
+    <t>Muestra Coagulada</t>
   </si>
 </sst>
 </file>
@@ -16769,10 +16769,10 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="196" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="B1" s="197" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="C1" s="197" t="s">
         <v>1355</v>
@@ -16806,7 +16806,7 @@
         <v>1349</v>
       </c>
       <c r="D3" s="202" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16828,13 +16828,13 @@
         <v>1348</v>
       </c>
       <c r="B5" s="201" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="C5" s="201" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="D5" s="202" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -16842,13 +16842,13 @@
         <v>1348</v>
       </c>
       <c r="B6" s="201" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="C6" s="201" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="D6" s="202" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -16856,13 +16856,13 @@
         <v>1348</v>
       </c>
       <c r="B7" s="201" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="C7" s="201" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="D7" s="202" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -16870,13 +16870,13 @@
         <v>1348</v>
       </c>
       <c r="B8" s="201" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="C8" s="201" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="D8" s="202" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -16898,10 +16898,10 @@
         <v>1337</v>
       </c>
       <c r="B10" s="201" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="C10" s="201" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="D10" s="202" t="s">
         <v>1341</v>
@@ -16912,7 +16912,7 @@
         <v>1337</v>
       </c>
       <c r="B11" s="201" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="C11" s="201" t="s">
         <v>1340</v>
@@ -16929,10 +16929,10 @@
         <v>1338</v>
       </c>
       <c r="C12" s="201" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="D12" s="202" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16954,7 +16954,7 @@
         <v>1337</v>
       </c>
       <c r="B14" s="201" t="s">
-        <v>3179</v>
+        <v>3200</v>
       </c>
       <c r="C14" s="201" t="s">
         <v>3178</v>
@@ -17010,7 +17010,7 @@
         <v>1337</v>
       </c>
       <c r="B18" s="206" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="C18" s="207" t="s">
         <v>2955</v>

--- a/APP lab archipielago 2.xlsx
+++ b/APP lab archipielago 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matias Zuñiga\Phyton lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7211BC-1C94-424E-97A2-36E469F74550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CB63D1-E681-4D95-AE2D-C96D6F7120E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9697,10 +9697,6 @@
     <t>Entrega Presencial de Resultados de examen</t>
   </si>
   <si>
-    <t>11:00 am - 13:00 pm
-16:00 pm - 18:00 pm</t>
-  </si>
-  <si>
     <t>Ordenes</t>
   </si>
   <si>
@@ -9772,6 +9768,10 @@
   </si>
   <si>
     <t>Fecha de nacimiento, RUT, Sexo ( se ingresa una nueva orden)</t>
+  </si>
+  <si>
+    <t>11:00 am - 13:00 pm /
+16:00 pm - 18:00 pm</t>
   </si>
 </sst>
 </file>
@@ -17150,64 +17150,64 @@
     </row>
     <row r="41" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="199" t="s">
+        <v>3177</v>
+      </c>
+      <c r="B41" s="199" t="s">
         <v>3178</v>
-      </c>
-      <c r="B41" s="199" t="s">
-        <v>3179</v>
       </c>
       <c r="C41" s="200"/>
     </row>
     <row r="42" spans="1:3" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="210" t="s">
+        <v>3179</v>
+      </c>
+      <c r="B42" s="208" t="s">
         <v>3180</v>
-      </c>
-      <c r="B42" s="208" t="s">
-        <v>3181</v>
       </c>
       <c r="C42" s="209"/>
     </row>
     <row r="43" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="210" t="s">
+        <v>3181</v>
+      </c>
+      <c r="B43" s="208" t="s">
         <v>3182</v>
-      </c>
-      <c r="B43" s="208" t="s">
-        <v>3183</v>
       </c>
       <c r="C43" s="209"/>
     </row>
     <row r="44" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="206" t="s">
+        <v>3188</v>
+      </c>
+      <c r="B44" s="208" t="s">
         <v>3189</v>
-      </c>
-      <c r="B44" s="208" t="s">
-        <v>3190</v>
       </c>
       <c r="C44" s="207"/>
     </row>
     <row r="45" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="210" t="s">
+        <v>3190</v>
+      </c>
+      <c r="B45" s="208" t="s">
         <v>3191</v>
-      </c>
-      <c r="B45" s="208" t="s">
-        <v>3192</v>
       </c>
       <c r="C45" s="209"/>
     </row>
     <row r="46" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="211" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B46" s="210" t="s">
         <v>3197</v>
-      </c>
-      <c r="B46" s="210" t="s">
-        <v>3198</v>
       </c>
       <c r="C46" s="209"/>
     </row>
     <row r="47" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="211" t="s">
+        <v>3198</v>
+      </c>
+      <c r="B47" s="212" t="s">
         <v>3199</v>
-      </c>
-      <c r="B47" s="212" t="s">
-        <v>3200</v>
       </c>
       <c r="C47" s="207"/>
     </row>
@@ -17307,7 +17307,7 @@
         <v>1372</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17329,13 +17329,13 @@
         <v>1365</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>1357</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17343,13 +17343,13 @@
         <v>1364</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>1357</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -17363,7 +17363,7 @@
         <v>1357</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -17385,7 +17385,7 @@
         <v>3176</v>
       </c>
       <c r="B12" s="205" t="s">
-        <v>3177</v>
+        <v>3200</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>1357</v>
@@ -17424,13 +17424,13 @@
     </row>
     <row r="15" spans="1:4" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>3193</v>
+      </c>
+      <c r="B15" s="205" t="s">
         <v>3194</v>
       </c>
-      <c r="B15" s="205" t="s">
+      <c r="C15" s="7" t="s">
         <v>3195</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>3196</v>
       </c>
       <c r="D15" s="6"/>
     </row>
